--- a/authorization_forms/015_corporate_expense_disclosure_consent_form--authorization_forms.xlsx
+++ b/authorization_forms/015_corporate_expense_disclosure_consent_form--authorization_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -918,8 +918,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'monthly',_'value':_1}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Monthly', 'value': 1}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'quarterly',_'value':_2}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Quarterly', 'value': 2}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'semi-annually',_'value':_3}</t>
+          <t>semi-annually</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Semi-Annually', 'value': 3}</t>
+          <t>Semi-Annually</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'annually',_'value':_4}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Annually', 'value': 4}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'business_travel',_'value':_1}</t>
+          <t>business_travel</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Business Travel', 'value': 1}</t>
+          <t>Business Travel</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'entertainment',_'value':_2}</t>
+          <t>entertainment</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Entertainment', 'value': 2}</t>
+          <t>Entertainment</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'meal_and_incidentals',_'value':_3}</t>
+          <t>meal_and_incidentals</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Meal and Incidentals', 'value': 3}</t>
+          <t>Meal and Incidentals</t>
         </is>
       </c>
     </row>
